--- a/docs/office wise asset list.xlsx
+++ b/docs/office wise asset list.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b2581325a3935e0/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Development\projects\it-inventory-final\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="11_F25DC773A252ABDACC104889411E636A5BDE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01D646BF-864C-468D-B692-97E94B263E6A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC1E2151-E6DC-4ADD-BC60-068BD46C9D3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="49">
   <si>
     <t>Holder</t>
   </si>
@@ -172,6 +172,9 @@
   </si>
   <si>
     <t>4003dn</t>
+  </si>
+  <si>
+    <t>Serial Number</t>
   </si>
 </sst>
 </file>
@@ -270,7 +273,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -279,6 +282,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
@@ -565,19 +571,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.85546875" customWidth="1"/>
     <col min="4" max="4" width="17.7109375" customWidth="1"/>
-    <col min="6" max="6" width="15.42578125" customWidth="1"/>
-    <col min="7" max="7" width="16.5703125" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="8.140625" customWidth="1"/>
-    <col min="10" max="10" width="19.7109375" customWidth="1"/>
+    <col min="6" max="6" width="16.5703125" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
+    <col min="8" max="8" width="8.140625" customWidth="1"/>
+    <col min="9" max="10" width="19.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -594,94 +600,100 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    </row>
+    <row r="2" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="4"/>
+      <c r="K2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="2" t="s">
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="4"/>
+      <c r="K3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="2" t="s">
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="4"/>
+      <c r="K4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>27</v>
       </c>
@@ -698,136 +710,142 @@
         <v>13</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="3" t="s">
+    </row>
+    <row r="6" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="G6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" s="4"/>
+      <c r="K6" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="H7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="I7" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6" s="2" t="s">
+      <c r="J7" s="4"/>
+      <c r="K7" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="J6" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" s="2" t="s">
+      <c r="I8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J8" s="4"/>
+      <c r="K8" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="2" t="s">
+      <c r="I9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J9" s="4"/>
+      <c r="K9" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2" t="s">
+    </row>
+    <row r="10" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J9" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="75" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="2" t="s">
+      <c r="I10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J10" s="4"/>
+      <c r="K10" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="G3:G4"/>
     <mergeCell ref="A6:A10"/>
     <mergeCell ref="B6:B10"/>
     <mergeCell ref="C6:C10"/>
@@ -838,7 +856,7 @@
     <mergeCell ref="C2:C4"/>
     <mergeCell ref="D2:D4"/>
     <mergeCell ref="E2:E4"/>
-    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="F3:F4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
